--- a/experiment_results/wedos_grid/rtt_bursts_S2_atk0.5pct_wu500000_stage1b_rep1.xlsx
+++ b/experiment_results/wedos_grid/rtt_bursts_S2_atk0.5pct_wu500000_stage1b_rep1.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -548,12 +548,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -605,12 +605,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -630,12 +630,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1441</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -662,12 +662,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -719,12 +719,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -776,12 +776,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -833,12 +833,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -947,12 +947,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -972,7 +972,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>20185</t>
+          <t>19909</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1004,12 +1004,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>40627</t>
+          <t>22955</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1061,12 +1061,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>39761</t>
+          <t>19043</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1118,12 +1118,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>104167</t>
+          <t>87362</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>198203</t>
+          <t>113079</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>345450</t>
+          <t>234609</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>464670</t>
+          <t>232298</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1346,12 +1346,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>464478</t>
+          <t>234417</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1403,12 +1403,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>457027</t>
+          <t>224847</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1460,17 +1460,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>446929</t>
+          <t>224318</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1517,24 +1517,24 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
           <t>1.86</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>0.06</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>1.86</t>
-        </is>
-      </c>
       <c r="H20" t="inlineStr">
         <is>
           <t>Não</t>
@@ -1542,7 +1542,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>446399</t>
+          <t>224318</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
